--- a/data/trans_camb/P37-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P37-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 7,19</t>
+          <t>-3,07; 7,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 6,71</t>
+          <t>-2,97; 6,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19,17; 29,38</t>
+          <t>18,71; 29,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 4,25</t>
+          <t>-6,07; 4,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 6,34</t>
+          <t>-4,59; 6,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,59; 29,34</t>
+          <t>18,63; 28,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 4,25</t>
+          <t>-2,58; 4,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 5,34</t>
+          <t>-1,69; 4,99</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>20,19; 28,0</t>
+          <t>20,34; 28,17</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-18,45; 64,1</t>
+          <t>-20,05; 64,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-20,85; 57,26</t>
+          <t>-19,91; 61,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>118,83; 269,41</t>
+          <t>116,02; 276,56</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-41,93; 41,9</t>
+          <t>-41,26; 45,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-29,2; 66,12</t>
+          <t>-31,52; 65,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>114,45; 307,93</t>
+          <t>114,09; 309,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-21,16; 37,76</t>
+          <t>-17,97; 38,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-14,33; 45,69</t>
+          <t>-12,05; 44,08</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>133,42; 254,36</t>
+          <t>128,12; 249,61</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 9,26</t>
+          <t>-2,72; 9,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 3,21</t>
+          <t>-7,77; 2,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15,3; 27,02</t>
+          <t>15,02; 27,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 6,65</t>
+          <t>-1,42; 7,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 6,17</t>
+          <t>-2,39; 5,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,92; 28,38</t>
+          <t>18,7; 27,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 7,19</t>
+          <t>-0,47; 7,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 3,06</t>
+          <t>-3,45; 3,09</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18,63; 26,33</t>
+          <t>18,82; 26,64</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-13,65; 68,67</t>
+          <t>-15,68; 72,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-39,75; 25,76</t>
+          <t>-41,38; 22,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>80,16; 206,77</t>
+          <t>79,81; 216,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-27,51; 124,31</t>
+          <t>-19,65; 136,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-23,48; 125,02</t>
+          <t>-27,26; 113,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>199,17; 598,57</t>
+          <t>193,48; 564,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 75,75</t>
+          <t>-3,73; 72,91</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-29,67; 30,44</t>
+          <t>-26,24; 30,55</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>140,4; 277,04</t>
+          <t>142,45; 287,42</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,24; 9,6</t>
+          <t>0,99; 9,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,67; 9,02</t>
+          <t>0,29; 9,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 21,13</t>
+          <t>-6,23; 21,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 6,67</t>
+          <t>-6,47; 6,39</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 13,03</t>
+          <t>-3,55; 12,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,11; 34,28</t>
+          <t>19,29; 34,75</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,2; 7,46</t>
+          <t>0,1; 7,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,79; 8,63</t>
+          <t>0,78; 8,68</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 23,04</t>
+          <t>-1,89; 22,71</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,65; 89,75</t>
+          <t>6,36; 91,41</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,64; 87,4</t>
+          <t>2,03; 87,37</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-36,79; 176,59</t>
+          <t>-40,71; 183,74</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-41,43; 78,74</t>
+          <t>-41,07; 81,28</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-23,48; 141,91</t>
+          <t>-23,69; 133,3</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>94,89; 382,67</t>
+          <t>111,31; 406,88</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,4; 70,35</t>
+          <t>0,66; 65,42</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,67; 76,92</t>
+          <t>4,64; 78,29</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-28,73; 195,61</t>
+          <t>-13,84; 190,46</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,34; 6,47</t>
+          <t>0,1; 6,49</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 3,54</t>
+          <t>-2,46; 3,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13,09; 20,46</t>
+          <t>13,34; 20,47</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 2,8</t>
+          <t>-4,62; 2,66</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 2,7</t>
+          <t>-4,2; 3,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,17; 58,73</t>
+          <t>16,99; 54,75</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 3,73</t>
+          <t>-1,01; 4,03</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 2,28</t>
+          <t>-2,35; 2,05</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>16,06; 40,37</t>
+          <t>16,33; 42,54</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,94; 42,65</t>
+          <t>0,44; 42,58</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-14,23; 23,21</t>
+          <t>-13,61; 24,08</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>73,83; 137,97</t>
+          <t>74,99; 136,06</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-28,66; 27,75</t>
+          <t>-30,48; 22,67</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-28,35; 25,36</t>
+          <t>-27,51; 26,75</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>115,74; 511,5</t>
+          <t>124,03; 500,98</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 26,78</t>
+          <t>-6,06; 28,7</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-14,91; 15,91</t>
+          <t>-14,34; 14,62</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>102,27; 279,57</t>
+          <t>105,15; 289,29</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 9,43</t>
+          <t>-0,43; 9,61</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 8,93</t>
+          <t>-0,27; 9,09</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,55; 18,32</t>
+          <t>7,73; 18,44</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,71; 10,02</t>
+          <t>1,39; 9,75</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 6,76</t>
+          <t>-1,42; 7,01</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,0; 22,92</t>
+          <t>9,14; 23,0</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,73; 8,3</t>
+          <t>2,02; 8,36</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,33; 6,55</t>
+          <t>0,33; 6,42</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>10,21; 19,63</t>
+          <t>9,76; 19,53</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>123,86%</t>
+          <t>123,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 81,64</t>
+          <t>-3,62; 82,14</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 78,51</t>
+          <t>-2,57; 79,15</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>42,69; 158,58</t>
+          <t>44,4; 163,23</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>9,87; 82,92</t>
+          <t>8,29; 85,32</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-11,62; 55,26</t>
+          <t>-9,16; 57,94</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>57,68; 185,26</t>
+          <t>60,71; 187,8</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,55; 67,72</t>
+          <t>12,22; 67,93</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>1,89; 52,29</t>
+          <t>1,76; 51,61</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>68,06; 156,65</t>
+          <t>65,23; 154,86</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,68; 9,25</t>
+          <t>0,24; 8,79</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 5,66</t>
+          <t>-1,49; 5,82</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 6,77</t>
+          <t>-2,32; 6,76</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1,39; 8,81</t>
+          <t>1,56; 8,83</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 7,08</t>
+          <t>-0,56; 6,83</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,55; 28,04</t>
+          <t>19,46; 27,49</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,16; 8,07</t>
+          <t>2,09; 8,18</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 5,75</t>
+          <t>-0,32; 5,49</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>13,82; 21,43</t>
+          <t>13,46; 20,95</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>6,02; 366,34</t>
+          <t>-3,08; 348,75</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-33,4; 232,82</t>
+          <t>-31,52; 232,25</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-47,43; 222,52</t>
+          <t>-46,04; 262,46</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>5,18; 42,23</t>
+          <t>6,67; 42,76</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 34,32</t>
+          <t>-2,36; 33,08</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>81,57; 136,09</t>
+          <t>80,51; 132,25</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>10,9; 47,42</t>
+          <t>10,47; 46,82</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 32,79</t>
+          <t>-1,68; 31,12</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>69,91; 123,28</t>
+          <t>68,96; 121,2</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1,97; 5,62</t>
+          <t>2,04; 5,55</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 3,56</t>
+          <t>0,19; 3,68</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>8,16; 18,12</t>
+          <t>9,3; 18,1</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,09</t>
+          <t>0,51; 4,32</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 3,18</t>
+          <t>-0,57; 3,36</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>18,93; 35,08</t>
+          <t>18,97; 36,57</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,65; 4,24</t>
+          <t>1,86; 4,29</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,77</t>
+          <t>0,35; 2,85</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>15,8; 25,43</t>
+          <t>15,93; 25,66</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>13,56; 43,15</t>
+          <t>13,97; 42,37</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 27,42</t>
+          <t>1,24; 28,68</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>58,8; 134,95</t>
+          <t>68,7; 135,47</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2,8; 26,94</t>
+          <t>2,9; 28,33</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 21,3</t>
+          <t>-3,43; 22,55</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>115,41; 229,69</t>
+          <t>116,83; 229,42</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>10,49; 29,59</t>
+          <t>12,03; 30,07</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>1,39; 19,41</t>
+          <t>2,23; 19,99</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>103,82; 171,47</t>
+          <t>105,29; 177,11</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P37-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P37-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24,42</t>
+          <t>24,22</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,22 +649,22 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>24,21</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0,69</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1,38</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>24,13</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,69</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1,38</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>24,2</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 7,07</t>
+          <t>-2,88; 6,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 6,88</t>
+          <t>-3,34; 6,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,71; 29,66</t>
+          <t>19,33; 29,9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,07; 4,32</t>
+          <t>-5,87; 4,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 6,45</t>
+          <t>-4,13; 6,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,63; 28,92</t>
+          <t>18,54; 29,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 4,45</t>
+          <t>-2,77; 4,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 4,99</t>
+          <t>-2,1; 5,17</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>20,34; 28,17</t>
+          <t>20,43; 27,92</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>182,32%</t>
+          <t>180,8%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>196,13%</t>
+          <t>196,78%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>186,64%</t>
+          <t>186,09%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-20,05; 64,78</t>
+          <t>-18,78; 59,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-19,91; 61,28</t>
+          <t>-23,34; 58,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>116,02; 276,56</t>
+          <t>121,01; 274,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-41,26; 45,1</t>
+          <t>-38,62; 52,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-31,52; 65,59</t>
+          <t>-28,63; 71,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>114,09; 309,87</t>
+          <t>113,03; 321,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-17,97; 38,42</t>
+          <t>-18,66; 40,06</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-12,05; 44,08</t>
+          <t>-14,55; 47,72</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>128,12; 249,61</t>
+          <t>133,35; 253,37</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>21,27</t>
+          <t>21,45</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>23,36</t>
+          <t>23,34</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>22,62</t>
+          <t>22,65</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 9,43</t>
+          <t>-3,28; 8,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,77; 2,78</t>
+          <t>-7,5; 2,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15,02; 27,19</t>
+          <t>14,98; 26,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 7,23</t>
+          <t>-1,97; 6,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 5,85</t>
+          <t>-1,88; 5,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,7; 27,66</t>
+          <t>18,41; 28,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 7,12</t>
+          <t>-0,36; 6,98</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 3,09</t>
+          <t>-3,53; 3,26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18,82; 26,64</t>
+          <t>18,55; 26,61</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>134,14%</t>
+          <t>135,3%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>334,98%</t>
+          <t>334,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>198,59%</t>
+          <t>198,87%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-15,68; 72,35</t>
+          <t>-17,66; 63,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-41,38; 22,68</t>
+          <t>-40,32; 22,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>79,81; 216,45</t>
+          <t>75,32; 202,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-19,65; 136,59</t>
+          <t>-24,16; 129,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-27,26; 113,91</t>
+          <t>-23,61; 107,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>193,48; 564,5</t>
+          <t>197,39; 591,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 72,91</t>
+          <t>-3,69; 68,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-26,24; 30,55</t>
+          <t>-27,36; 33,0</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>142,45; 287,42</t>
+          <t>135,03; 276,65</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7,87</t>
+          <t>19,11</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>26,82</t>
+          <t>26,28</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11,65</t>
+          <t>21,15</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,99; 9,57</t>
+          <t>1,2; 9,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,29; 9,11</t>
+          <t>0,29; 8,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 21,26</t>
+          <t>14,01; 23,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 6,39</t>
+          <t>-6,86; 5,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 12,29</t>
+          <t>-2,81; 14,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,29; 34,75</t>
+          <t>18,19; 33,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,1; 7,04</t>
+          <t>0,37; 7,1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,78; 8,68</t>
+          <t>0,84; 8,61</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 22,71</t>
+          <t>16,92; 25,25</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>153,0%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>213,24%</t>
+          <t>208,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>169,08%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,36; 91,41</t>
+          <t>6,89; 87,28</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,03; 87,37</t>
+          <t>0,87; 80,54</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-40,71; 183,74</t>
+          <t>94,29; 222,06</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-41,07; 81,28</t>
+          <t>-43,34; 68,2</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-23,69; 133,3</t>
+          <t>-21,46; 155,93</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>111,31; 406,88</t>
+          <t>103,19; 384,22</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,66; 65,42</t>
+          <t>3,09; 67,04</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,64; 78,29</t>
+          <t>5,78; 80,38</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-13,84; 190,46</t>
+          <t>115,2; 238,06</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16,96</t>
+          <t>17,02</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,38</t>
+          <t>17,25</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>24,04</t>
+          <t>16,89</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,1; 6,49</t>
+          <t>0,2; 6,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 3,57</t>
+          <t>-2,2; 3,69</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13,34; 20,47</t>
+          <t>13,59; 20,43</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 2,66</t>
+          <t>-4,42; 2,38</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 3,15</t>
+          <t>-3,82; 3,65</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,99; 54,75</t>
+          <t>13,39; 20,74</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 4,03</t>
+          <t>-0,9; 3,79</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 2,05</t>
+          <t>-2,33; 2,07</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>16,33; 42,54</t>
+          <t>14,34; 19,34</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>103,13%</t>
+          <t>103,47%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>249,02%</t>
+          <t>132,63%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>158,3%</t>
+          <t>111,2%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,44; 42,58</t>
+          <t>1,17; 41,57</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-13,61; 24,08</t>
+          <t>-12,12; 25,18</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>74,99; 136,06</t>
+          <t>75,38; 135,59</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-30,48; 22,67</t>
+          <t>-29,43; 21,53</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-27,51; 26,75</t>
+          <t>-26,26; 32,06</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>124,03; 500,98</t>
+          <t>89,28; 188,76</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 28,7</t>
+          <t>-5,48; 26,75</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-14,34; 14,62</t>
+          <t>-14,2; 14,43</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>105,15; 289,29</t>
+          <t>86,63; 136,87</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>12,99</t>
+          <t>10,59</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,58</t>
+          <t>21,17</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>15,92</t>
+          <t>16,87</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 9,61</t>
+          <t>-0,89; 9,48</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 9,09</t>
+          <t>-0,67; 8,92</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,73; 18,44</t>
+          <t>5,68; 15,88</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,39; 9,75</t>
+          <t>1,57; 9,81</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 7,01</t>
+          <t>-1,61; 6,83</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,14; 23,0</t>
+          <t>17,18; 25,43</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,02; 8,36</t>
+          <t>1,87; 8,1</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,33; 6,42</t>
+          <t>0,24; 6,58</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9,76; 19,53</t>
+          <t>13,81; 20,24</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>74,87%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>123,85%</t>
+          <t>149,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>112,34%</t>
+          <t>119,02%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 82,14</t>
+          <t>-4,95; 87,54</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 79,15</t>
+          <t>-3,16; 82,1</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>44,4; 163,23</t>
+          <t>32,44; 137,07</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8,29; 85,32</t>
+          <t>9,76; 83,05</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-9,16; 57,94</t>
+          <t>-9,8; 56,59</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>60,71; 187,8</t>
+          <t>100,19; 222,81</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,22; 67,93</t>
+          <t>12,2; 65,46</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>1,76; 51,61</t>
+          <t>1,45; 53,07</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>65,23; 154,86</t>
+          <t>86,19; 166,09</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1,36</t>
+          <t>0,95</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>23,82</t>
+          <t>22,71</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>17,57</t>
+          <t>17,44</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,24; 8,79</t>
+          <t>0,23; 8,77</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 5,82</t>
+          <t>-1,73; 5,78</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 6,76</t>
+          <t>-2,58; 5,37</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1,56; 8,83</t>
+          <t>1,16; 8,65</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 6,83</t>
+          <t>-0,69; 6,89</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,46; 27,49</t>
+          <t>18,77; 26,54</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,09; 8,18</t>
+          <t>1,94; 8,07</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 5,49</t>
+          <t>-0,77; 5,47</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>13,46; 20,95</t>
+          <t>14,0; 21,05</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>107,3%</t>
+          <t>102,26%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,24%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 348,75</t>
+          <t>0,75; 324,89</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-31,52; 232,25</t>
+          <t>-35,7; 222,47</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-46,04; 262,46</t>
+          <t>-49,78; 214,85</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>6,67; 42,76</t>
+          <t>4,75; 41,86</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 33,08</t>
+          <t>-2,92; 33,9</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>80,51; 132,25</t>
+          <t>78,1; 130,83</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>10,47; 46,82</t>
+          <t>9,35; 46,54</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 31,12</t>
+          <t>-4,01; 30,99</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>68,96; 121,2</t>
+          <t>68,12; 120,22</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>15,2</t>
+          <t>17,1</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>23,46</t>
+          <t>20,26</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>19,46</t>
+          <t>18,73</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2,04; 5,55</t>
+          <t>1,83; 5,63</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,19; 3,68</t>
+          <t>0,05; 3,64</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>9,3; 18,1</t>
+          <t>15,17; 19,09</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,32</t>
+          <t>0,49; 4,12</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 3,36</t>
+          <t>-0,33; 3,29</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>18,97; 36,57</t>
+          <t>18,53; 22,28</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,86; 4,29</t>
+          <t>1,84; 4,34</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,85</t>
+          <t>0,34; 2,82</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>15,93; 25,66</t>
+          <t>17,44; 20,2</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>109,29%</t>
+          <t>122,99%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>147,95%</t>
+          <t>127,76%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>130,63%</t>
+          <t>125,75%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>13,97; 42,37</t>
+          <t>12,52; 42,96</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>1,24; 28,68</t>
+          <t>0,32; 28,12</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>68,7; 135,47</t>
+          <t>102,06; 146,54</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2,9; 28,33</t>
+          <t>2,9; 27,88</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 22,55</t>
+          <t>-2,08; 22,07</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>116,83; 229,42</t>
+          <t>109,51; 150,89</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>12,03; 30,07</t>
+          <t>11,77; 30,66</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>2,23; 19,99</t>
+          <t>2,06; 19,83</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>105,29; 177,11</t>
+          <t>111,56; 142,25</t>
         </is>
       </c>
     </row>
